--- a/M2. Statistica & Excel/PraticaW1D4_GGabriele.xlsx
+++ b/M2. Statistica & Excel/PraticaW1D4_GGabriele.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\Desktop\Epicode-Dapt0326\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gabri\Desktop\Epicode-Dapt0326\M2. Statistica &amp; Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BB8ADC0-74EE-4219-AB01-1CF1E41E3F78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5D39CBA-2D77-4766-9F5B-492C28F0986E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{82F25D09-57DB-4D96-801F-99FA20AF9E91}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{82F25D09-57DB-4D96-801F-99FA20AF9E91}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -757,7 +757,7 @@
         <v>2</v>
       </c>
       <c r="E24" s="3">
-        <f t="shared" ref="E23:E24" si="3">_xlfn.NORM.S.DIST(D24,TRUE)</f>
+        <f t="shared" ref="E24" si="3">_xlfn.NORM.S.DIST(D24,TRUE)</f>
         <v>0.97724986805182079</v>
       </c>
       <c r="G24" t="s">
